--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6005-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6005-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33A110A2-22BC-4940-A90B-E4C1D9CF54C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{496945EA-237D-42B2-BFA4-FDA69A5AD70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1CD3C99D-EC6B-4995-BA43-27547F03CB0C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A5B4136C-EB5F-4863-87D9-BBE07DA78731}"/>
   </bookViews>
   <sheets>
     <sheet name="6005-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1493,27 +1493,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F061C1-C0A5-4376-91F3-B52A2CA2531C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15363293-4D5E-44BF-83AB-44003B3D5A76}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +1546,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +1582,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1635,7 +1634,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1703,7 +1702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1991,7 +1990,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2207,7 +2206,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2423,7 +2422,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2495,7 +2494,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2567,7 +2566,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2711,7 +2710,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2855,7 +2854,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2927,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3071,7 +3070,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3215,7 +3214,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3359,7 +3358,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3503,7 +3502,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1999</v>
       </c>
@@ -3575,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1998</v>
       </c>
@@ -3647,7 +3646,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1997</v>
       </c>
@@ -3719,7 +3718,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>1996</v>
       </c>
@@ -3791,7 +3790,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>1995</v>
       </c>
@@ -3863,7 +3862,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>1994</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1993</v>
       </c>
@@ -4007,7 +4006,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>1992</v>
       </c>
@@ -4079,7 +4078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>57</v>
       </c>
